--- a/Дело3а-78-2026Таганай/13_Путевые_листы/13.1 Путевые листы 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/13.1 Путевые листы 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92545164636</v>
+        <v>46157.93120856829</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/13.1 Путевые листы 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/13.1 Путевые листы 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93120856829</v>
+        <v>46157.93372074074</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/13.1 Путевые листы 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/13.1 Путевые листы 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93372074074</v>
+        <v>46157.93678689618</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/13.1 Путевые листы 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/13.1 Путевые листы 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93678689618</v>
+        <v>46158.28198100645</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/13.1 Путевые листы 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/13.1 Путевые листы 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28198100645</v>
+        <v>46158.29724124895</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/13.1 Путевые листы 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/13.1 Путевые листы 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29724124895</v>
+        <v>46158.29794872647</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/13.1 Путевые листы 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/13.1 Путевые листы 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29794872647</v>
+        <v>46158.33359484732</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/13.1 Путевые листы 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/13.1 Путевые листы 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33359484732</v>
+        <v>46158.37212984885</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/13_Путевые_листы/13.1 Путевые листы 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/13_Путевые_листы/13.1 Путевые листы 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37212984885</v>
+        <v>46158.37269729589</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
